--- a/artfynd/A 39308-2024 artfynd.xlsx
+++ b/artfynd/A 39308-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120249218</v>
       </c>
       <c r="B2" t="n">
-        <v>109824</v>
+        <v>109848</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>120248915</v>
       </c>
       <c r="B3" t="n">
-        <v>105009</v>
+        <v>105032</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>120248982</v>
       </c>
       <c r="B4" t="n">
-        <v>57679</v>
+        <v>57689</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>120249229</v>
       </c>
       <c r="B5" t="n">
-        <v>57463</v>
+        <v>57473</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>120249827</v>
       </c>
       <c r="B6" t="n">
-        <v>94681</v>
+        <v>94704</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 39308-2024 artfynd.xlsx
+++ b/artfynd/A 39308-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120249218</v>
+        <v>120248915</v>
       </c>
       <c r="B2" t="n">
-        <v>109848</v>
+        <v>105032</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219677</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592186</v>
+        <v>592223</v>
       </c>
       <c r="R2" t="n">
-        <v>6393354</v>
+        <v>6393314</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120248915</v>
+        <v>120249827</v>
       </c>
       <c r="B3" t="n">
-        <v>105032</v>
+        <v>94704</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,46 +812,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Flodhem, Flodhem, Sm</t>
+          <t>Kvarnkärr, Kvarnkärr, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592223</v>
+        <v>592078</v>
       </c>
       <c r="R3" t="n">
-        <v>6393314</v>
+        <v>6393496</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120248982</v>
+        <v>120249229</v>
       </c>
       <c r="B4" t="n">
-        <v>57689</v>
+        <v>57473</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,25 +920,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -962,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592211</v>
+        <v>592187</v>
       </c>
       <c r="R4" t="n">
-        <v>6393326</v>
+        <v>6393352</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -997,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120249229</v>
+        <v>120249218</v>
       </c>
       <c r="B5" t="n">
-        <v>57473</v>
+        <v>109848</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,31 +1037,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>219677</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1079,13 +1074,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592187</v>
+        <v>592186</v>
       </c>
       <c r="R5" t="n">
-        <v>6393352</v>
+        <v>6393354</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1114,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1119,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120249827</v>
+        <v>120248982</v>
       </c>
       <c r="B6" t="n">
-        <v>94704</v>
+        <v>57689</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,37 +1162,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kvarnkärr, Kvarnkärr, Sm</t>
+          <t>Flodhem, Flodhem, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592078</v>
+        <v>592211</v>
       </c>
       <c r="R6" t="n">
-        <v>6393496</v>
+        <v>6393326</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 39308-2024 artfynd.xlsx
+++ b/artfynd/A 39308-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120248915</v>
+        <v>120249827</v>
       </c>
       <c r="B2" t="n">
-        <v>105032</v>
+        <v>94704</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,46 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Flodhem, Flodhem, Sm</t>
+          <t>Kvarnkärr, Kvarnkärr, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592223</v>
+        <v>592078</v>
       </c>
       <c r="R2" t="n">
-        <v>6393314</v>
+        <v>6393496</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120249827</v>
+        <v>120248982</v>
       </c>
       <c r="B3" t="n">
-        <v>94704</v>
+        <v>57689</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,37 +803,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kvarnkärr, Kvarnkärr, Sm</t>
+          <t>Flodhem, Flodhem, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592078</v>
+        <v>592211</v>
       </c>
       <c r="R3" t="n">
-        <v>6393496</v>
+        <v>6393326</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120249229</v>
+        <v>120249218</v>
       </c>
       <c r="B4" t="n">
-        <v>57473</v>
+        <v>109848</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,31 +916,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>219677</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -953,13 +953,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592187</v>
+        <v>592186</v>
       </c>
       <c r="R4" t="n">
-        <v>6393352</v>
+        <v>6393354</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120249218</v>
+        <v>120248915</v>
       </c>
       <c r="B5" t="n">
-        <v>109848</v>
+        <v>105032</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,26 +1041,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219677</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1074,13 +1074,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592186</v>
+        <v>592223</v>
       </c>
       <c r="R5" t="n">
-        <v>6393354</v>
+        <v>6393314</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120248982</v>
+        <v>120249229</v>
       </c>
       <c r="B6" t="n">
-        <v>57689</v>
+        <v>57473</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,25 +1158,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1191,10 +1191,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592211</v>
+        <v>592187</v>
       </c>
       <c r="R6" t="n">
-        <v>6393326</v>
+        <v>6393352</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 39308-2024 artfynd.xlsx
+++ b/artfynd/A 39308-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120249827</v>
+        <v>120248982</v>
       </c>
       <c r="B2" t="n">
-        <v>94704</v>
+        <v>57689</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kvarnkärr, Kvarnkärr, Sm</t>
+          <t>Flodhem, Flodhem, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592078</v>
+        <v>592211</v>
       </c>
       <c r="R2" t="n">
-        <v>6393496</v>
+        <v>6393326</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120248982</v>
+        <v>120249827</v>
       </c>
       <c r="B3" t="n">
-        <v>57689</v>
+        <v>94704</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,42 +808,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Flodhem, Flodhem, Sm</t>
+          <t>Kvarnkärr, Kvarnkärr, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592211</v>
+        <v>592078</v>
       </c>
       <c r="R3" t="n">
-        <v>6393326</v>
+        <v>6393496</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 39308-2024 artfynd.xlsx
+++ b/artfynd/A 39308-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120248982</v>
+        <v>120249218</v>
       </c>
       <c r="B2" t="n">
-        <v>57689</v>
+        <v>109848</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>219677</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592211</v>
+        <v>592186</v>
       </c>
       <c r="R2" t="n">
-        <v>6393326</v>
+        <v>6393354</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120249827</v>
+        <v>120249229</v>
       </c>
       <c r="B3" t="n">
-        <v>94704</v>
+        <v>57473</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,41 +808,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kvarnkärr, Kvarnkärr, Sm</t>
+          <t>Flodhem, Flodhem, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592078</v>
+        <v>592187</v>
       </c>
       <c r="R3" t="n">
-        <v>6393496</v>
+        <v>6393352</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120249218</v>
+        <v>120248915</v>
       </c>
       <c r="B4" t="n">
-        <v>109848</v>
+        <v>105032</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,26 +929,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219677</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -953,13 +962,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592186</v>
+        <v>592223</v>
       </c>
       <c r="R4" t="n">
-        <v>6393354</v>
+        <v>6393314</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -988,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120248915</v>
+        <v>120248982</v>
       </c>
       <c r="B5" t="n">
-        <v>105032</v>
+        <v>57689</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,31 +1050,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1074,13 +1079,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592223</v>
+        <v>592211</v>
       </c>
       <c r="R5" t="n">
-        <v>6393314</v>
+        <v>6393326</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,7 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120249229</v>
+        <v>120249827</v>
       </c>
       <c r="B6" t="n">
-        <v>57473</v>
+        <v>94704</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,46 +1163,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Flodhem, Flodhem, Sm</t>
+          <t>Kvarnkärr, Kvarnkärr, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592187</v>
+        <v>592078</v>
       </c>
       <c r="R6" t="n">
-        <v>6393352</v>
+        <v>6393496</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 39308-2024 artfynd.xlsx
+++ b/artfynd/A 39308-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120249218</v>
+        <v>120249827</v>
       </c>
       <c r="B2" t="n">
-        <v>109848</v>
+        <v>94704</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,46 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219677</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Flodhem, Flodhem, Sm</t>
+          <t>Kvarnkärr, Kvarnkärr, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592186</v>
+        <v>592078</v>
       </c>
       <c r="R2" t="n">
-        <v>6393354</v>
+        <v>6393496</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -1034,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120248982</v>
+        <v>120249218</v>
       </c>
       <c r="B5" t="n">
-        <v>57689</v>
+        <v>109848</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,27 +1041,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>219677</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1079,13 +1074,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592211</v>
+        <v>592186</v>
       </c>
       <c r="R5" t="n">
-        <v>6393326</v>
+        <v>6393354</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1114,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1119,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120249827</v>
+        <v>120248982</v>
       </c>
       <c r="B6" t="n">
-        <v>94704</v>
+        <v>57689</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,37 +1162,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kvarnkärr, Kvarnkärr, Sm</t>
+          <t>Flodhem, Flodhem, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592078</v>
+        <v>592211</v>
       </c>
       <c r="R6" t="n">
-        <v>6393496</v>
+        <v>6393326</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 39308-2024 artfynd.xlsx
+++ b/artfynd/A 39308-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120249229</v>
+        <v>120248915</v>
       </c>
       <c r="B3" t="n">
-        <v>57473</v>
+        <v>105032</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,31 +799,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592187</v>
+        <v>592223</v>
       </c>
       <c r="R3" t="n">
-        <v>6393352</v>
+        <v>6393314</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120248915</v>
+        <v>120249229</v>
       </c>
       <c r="B4" t="n">
-        <v>105032</v>
+        <v>57473</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,35 +920,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -953,13 +953,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592223</v>
+        <v>592187</v>
       </c>
       <c r="R4" t="n">
-        <v>6393314</v>
+        <v>6393352</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 39308-2024 artfynd.xlsx
+++ b/artfynd/A 39308-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120249827</v>
+        <v>120248915</v>
       </c>
       <c r="B2" t="n">
-        <v>94704</v>
+        <v>105032</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kvarnkärr, Kvarnkärr, Sm</t>
+          <t>Flodhem, Flodhem, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592078</v>
+        <v>592223</v>
       </c>
       <c r="R2" t="n">
-        <v>6393496</v>
+        <v>6393314</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120248915</v>
+        <v>120249229</v>
       </c>
       <c r="B3" t="n">
-        <v>105032</v>
+        <v>57473</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,35 +808,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -836,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592223</v>
+        <v>592187</v>
       </c>
       <c r="R3" t="n">
-        <v>6393314</v>
+        <v>6393352</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120249229</v>
+        <v>120248982</v>
       </c>
       <c r="B4" t="n">
-        <v>57473</v>
+        <v>57689</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,25 +925,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592187</v>
+        <v>592211</v>
       </c>
       <c r="R4" t="n">
-        <v>6393352</v>
+        <v>6393326</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -988,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120249218</v>
+        <v>120249827</v>
       </c>
       <c r="B5" t="n">
-        <v>109848</v>
+        <v>94704</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,46 +1046,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219677</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Flodhem, Flodhem, Sm</t>
+          <t>Kvarnkärr, Kvarnkärr, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592186</v>
+        <v>592078</v>
       </c>
       <c r="R5" t="n">
-        <v>6393354</v>
+        <v>6393496</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120248982</v>
+        <v>120249218</v>
       </c>
       <c r="B6" t="n">
-        <v>57689</v>
+        <v>109848</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,27 +1158,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>219677</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1191,13 +1191,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592211</v>
+        <v>592186</v>
       </c>
       <c r="R6" t="n">
-        <v>6393326</v>
+        <v>6393354</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 39308-2024 artfynd.xlsx
+++ b/artfynd/A 39308-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120248915</v>
+        <v>120249827</v>
       </c>
       <c r="B2" t="n">
-        <v>105032</v>
+        <v>94704</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,46 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Flodhem, Flodhem, Sm</t>
+          <t>Kvarnkärr, Kvarnkärr, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592223</v>
+        <v>592078</v>
       </c>
       <c r="R2" t="n">
-        <v>6393314</v>
+        <v>6393496</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120249229</v>
+        <v>120249218</v>
       </c>
       <c r="B3" t="n">
-        <v>57473</v>
+        <v>109848</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,31 +799,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>219677</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -841,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592187</v>
+        <v>592186</v>
       </c>
       <c r="R3" t="n">
-        <v>6393352</v>
+        <v>6393354</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1030,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120249827</v>
+        <v>120249229</v>
       </c>
       <c r="B5" t="n">
-        <v>94704</v>
+        <v>57473</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,41 +1037,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kvarnkärr, Kvarnkärr, Sm</t>
+          <t>Flodhem, Flodhem, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592078</v>
+        <v>592187</v>
       </c>
       <c r="R5" t="n">
-        <v>6393496</v>
+        <v>6393352</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120249218</v>
+        <v>120248915</v>
       </c>
       <c r="B6" t="n">
-        <v>109848</v>
+        <v>105032</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,26 +1158,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219677</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1191,13 +1191,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592186</v>
+        <v>592223</v>
       </c>
       <c r="R6" t="n">
-        <v>6393354</v>
+        <v>6393314</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
